--- a/xls/square_20_tri3_21.xlsx
+++ b/xls/square_20_tri3_21.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>484</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>441</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>2.5433621584552877</v>
+      </c>
+      <c r="J19">
+        <v>-0.8712174342002387</v>
+      </c>
+      <c r="K19">
+        <v>0.6766292884369559</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>484</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>441</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>1.0553983716297968</v>
+      </c>
+      <c r="J20">
+        <v>-1.7645758261158218</v>
+      </c>
+      <c r="K20">
+        <v>-0.14313729745954726</v>
+      </c>
+    </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>11</v>
